--- a/data/careops_phase1_expanded_synthetic_workbook.xlsx
+++ b/data/careops_phase1_expanded_synthetic_workbook.xlsx
@@ -21,7 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Examples" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Knowledge_Articles'!$A$1:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Knowledge_Articles'!$A$1:$I$158</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflows'!$A$1:$H$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Request_Types'!$A$1:$G$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Field_Definitions'!$A$1:$F$84</definedName>
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +76,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -112,6 +127,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -482,11 +506,11 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="105" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>CAREOPS — PHASE 1 EXPANDED SYNTHETIC DATA FOUNDATION</t>
@@ -494,7 +518,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr"/>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Dataset status</t>
@@ -502,11 +526,11 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Expanded synthetic dataset for hackathon development, testing and demonstration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Expanded synthetic dataset for hackathon development and testing. New knowledge entries are generic examples, not validated organizational policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Privacy</t>
@@ -514,11 +538,11 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>100% synthetic. No real patient, member, provider, employee, client or confidential production data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Synthetic demo content only. No real patient, member, provider, employee, client or confidential production data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Requests</t>
@@ -530,7 +554,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Knowledge</t>
@@ -538,11 +562,11 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>50 approved-style knowledge articles for RAG grounding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>157 approved-style synthetic knowledge articles for RAG grounding; new entries are generic templates and require local policy verification before production use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Workflows</t>
@@ -554,7 +578,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Routing</t>
@@ -566,7 +590,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Fields</t>
@@ -578,7 +602,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Audit</t>
@@ -590,7 +614,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Core safety</t>
@@ -602,7 +626,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Next phase</t>
@@ -32801,115 +32825,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="95" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>article_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>department</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>source_name</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>importance</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>KA-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>ID Card Replacement</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>employee services</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Employees with damaged or lost ID cards must submit an ID replacement request. The request requires employee ID, department, reason, and preferred contact method. HR verifies employment status before approving the request.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>HR Employee Services Policy v1.2</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>KA-002</t>
@@ -32956,54 +32980,54 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>KA-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Employee Profile Update</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>employee services</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Employees may request updates to non-sensitive profile fields such as preferred name, office location, or department display name. HR verifies the request before updating records.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>HR Profile Management v1.1</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>KA-004</t>
@@ -33050,54 +33074,54 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>KA-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Payroll Query Routing</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Payroll-specific or account-specific salary queries must be routed to Payroll Support after employee identity and request category are captured. The assistant must not expose payroll records.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Payroll Support SOP v2.2</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>KA-006</t>
@@ -33144,54 +33168,54 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>KA-007</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Application Access Request</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>access management</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Application access requires employee ID, department, application name, access type, and manager. IT Access Management reviews the request and obtains required approvals.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>IT Access Management v3.0</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>KA-008</t>
@@ -33238,54 +33262,54 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>KA-009</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Laptop Request</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Standard laptop requests require employee ID, department, role, manager, and business justification. Hardware allocation is subject to IT inventory and approval.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>IT Equipment Request v2.3</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="100" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>KA-010</t>
@@ -33332,54 +33356,54 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>KA-011</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Meeting Room Booking</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>facilities</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Employees can request a meeting room by providing date, start time, end time, expected attendees, and required room features. Final booking depends on room availability.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Facilities Booking Guide v2.4</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="100" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>KA-012</t>
@@ -33426,54 +33450,54 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>KA-013</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Access Badge Door Issue</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>physical access</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>A malfunctioning access badge reader should be routed to Facilities Security Support. Employees should provide building, floor, door/location, and approximate time of issue.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Physical Access Support v1.5</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="100" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>KA-014</t>
@@ -33520,54 +33544,54 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>KA-015</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Vendor Information Request</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>vendor support</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Vendor onboarding or vendor record questions must be routed to Procurement Operations. The assistant must not expose confidential vendor information.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Vendor Operations SOP v1.8</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="100" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>KA-016</t>
@@ -33614,54 +33638,54 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>KA-017</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Patient Information Boundary</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Privacy Office</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>privacy</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>The assistant must not disclose confidential patient information or retrieve patient-specific records. Requests involving protected or sensitive information require authorized human handling.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>Privacy &amp; Data Handling Policy v2.0</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="100" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>KA-018</t>
@@ -33708,54 +33732,54 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="20" ht="100" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>KA-019</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Urgent Facility Issue</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>urgent maintenance</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Safety-related facility issues such as smoke, exposed wiring, major water leakage, or blocked emergency routes should be marked urgent and immediately routed to Facilities/Safety personnel.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Facilities Emergency SOP v2.0</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="100" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>KA-020</t>
@@ -33802,54 +33826,54 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>KA-021</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Employee Onboarding Checklist</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>onboarding</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Standard onboarding includes employee profile confirmation, manager assignment, required access requests, ID card processing, and orientation scheduling. The assistant may explain the sequence but cannot mark onboarding complete without human confirmation.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>HR Onboarding Guide v2.1</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="100" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>KA-022</t>
@@ -33896,54 +33920,54 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="24" ht="100" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>KA-023</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Department Transfer</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>employee movement</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Department transfer requests require employee ID, current department, new department, effective date, and manager confirmation. HR reviews and updates the record.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>HR Employee Movement v1.7</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="100" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>KA-024</t>
@@ -33990,54 +34014,54 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="26" ht="100" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>KA-025</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Training Registration</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>training</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Routine internal training registration requires employee ID, course name, preferred session, and manager approval where applicable.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Learning Operations Guide v2.3</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="100" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>KA-026</t>
@@ -34084,54 +34108,54 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="28" ht="100" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>KA-027</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>MFA Enrollment</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Multi-factor authentication enrollment follows the approved IT security procedure. The assistant may provide instructions but must never request authentication secrets or one-time codes.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>IT Security SOP v5.4</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="100" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>KA-028</t>
@@ -34178,54 +34202,54 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="30" ht="100" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>KA-029</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Shared Drive Access</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>access management</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Shared drive access requires employee ID, department, drive name, requested access level, and manager approval. IT reviews authorization.</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>File Access SOP v2.7</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="100" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>KA-030</t>
@@ -34272,54 +34296,54 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="32" ht="100" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>KA-031</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Email Distribution List</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>communication tools</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Requests to join or create an organizational distribution list require employee ID, list name, business justification, and manager approval where required.</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Messaging Administration SOP v2.2</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="100" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>KA-032</t>
@@ -34366,54 +34390,54 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="34" ht="100" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>KA-033</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Visitor Registration</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Visitor registration requires host name, visitor name, visit date, expected arrival time, and purpose. Security validates the request.</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>Visitor Management SOP v2.6</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="100" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>KA-034</t>
@@ -34460,54 +34484,54 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="36" ht="100" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>KA-035</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Office Move Request</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>workspace</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Office move requests require requester ID, current location, destination location, requested move date, and equipment details.</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>Workspace Move SOP v2.1</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="100" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>KA-036</t>
@@ -34554,54 +34578,54 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="38" ht="100" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>KA-037</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Catering Request</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Routine internal catering requests require event date, location, attendee count, dietary requirements, and requester details. Final arrangements require human confirmation.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>Facilities Events SOP v1.8</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="100" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>KA-038</t>
@@ -34648,54 +34672,54 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="40" ht="100" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>KA-039</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Quote Request</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>purchasing</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>Quote requests require item description, quantity, required-by date, department, and business justification. Procurement coordinates vendor engagement.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>Procurement Sourcing SOP v2.4</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="100" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>KA-040</t>
@@ -34742,54 +34766,54 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="42" ht="100" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>KA-041</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Expense Claim Guidance</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>expense</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>The assistant may explain the approved expense claim process. Individual claim status or financial records require authorized Finance handling.</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>Expense Operations Guide v3.0</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="100" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>KA-042</t>
@@ -34836,54 +34860,54 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="44" ht="100" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>KA-043</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Travel Change Request</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Travel Desk</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Changes to existing travel arrangements require the request identifier, requested change, travel date, and requester identity. Human travel support handles modifications.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Corporate Travel SOP v2.6</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="100" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>KA-044</t>
@@ -34930,54 +34954,54 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="46" ht="100" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>KA-045</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Lost Property</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Lost property reports require location, approximate time, item description, and contact method. Security handles recovery and custody.</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>Security Services Guide v1.9</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="100" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>KA-046</t>
@@ -35024,54 +35048,54 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="48" ht="100" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>KA-047</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Service Status Inquiry</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>service status</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>Routine questions about known operational service interruptions may be answered from the approved status information. If no current approved status exists, route to Operations Support.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>Operations Service Status v1.4</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="100" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>KA-048</t>
@@ -35118,54 +35142,54 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="50" ht="100" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>KA-049</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Data Export Request</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Privacy Office</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>data handling</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Requests to export operational or personal data require authorization and human review. The assistant must not directly export confidential records.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Data Handling SOP v3.1</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="100" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>KA-050</t>
@@ -35212,8 +35236,5572 @@
         </is>
       </c>
     </row>
+    <row r="52" ht="100" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>KA-051</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Annual Leave Request Guidance</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request annual leave.
+Common questions: annual leave request guidance | How do I request annual leave? | What should I do if I need to request annual leave? | How can I request help with annual leave request guidance? | Who handles annual leave request guidance?
+Guidance: Check the current leave policy and available balance through the approved HR channel. Submit requested dates, leave category, handover plan if required, and manager details. Wait for the authorized manager or HR decision before treating leave as approved.
+Information to include: employee identifier, leave category, start and end dates, manager, handover notes if required.
+Safety and approval: Leave eligibility, balance, notice periods, and approval rules must come from the current HR policy; the assistant must not approve leave.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="100" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>KA-052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Sick Leave Documentation</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask about sick leave documentation.
+Common questions: sick leave documentation | How do I ask about sick leave documentation? | What should I do if I need to ask about sick leave documentation? | How can I request help with sick leave documentation? | Who handles sick leave documentation?
+Guidance: Review the current HR sick-leave policy and submit only documentation explicitly required by that policy through the approved private channel. Tell the manager about absence using the normal notification process.
+Information to include: absence dates, contact method, required policy reference; sensitive medical details only through an authorized channel if strictly required.
+Safety and approval: Do not request or expose diagnoses or detailed medical records in the general assistant; HR handles policy questions and authorized confidential channels.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="100" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>KA-053</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Parental Leave Information</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: find parental leave information.
+Common questions: parental leave information | How do I find parental leave information? | What should I do if I need to find parental leave information? | How can I request help with parental leave information? | Who handles parental leave information?
+Guidance: Ask HR for the current eligibility, duration, notice, documents, and approval rules. Submit a formal request through the designated HR process and retain its reference number.
+Information to include: employee identifier, expected leave dates, contact method, required documents as specified by HR.
+Safety and approval: Do not invent legal entitlement or policy deadlines; verify current policy and applicable law with HR.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="100" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>KA-054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Payslip Access Problem</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>payroll</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a payslip access problem.
+Common questions: payslip access problem | How do I report a payslip access problem? | What should I do if I need to report a payslip access problem? | How can I request help with payslip access problem? | Who handles payslip access problem?
+Guidance: Confirm the correct employee portal and reporting period. If access fails, submit a payroll support request; if the payslip appears incorrect, identify the pay period and the discrepancy category without posting bank details in chat.
+Information to include: employee identifier, pay period, issue category, safe contact method.
+Safety and approval: Payroll records are confidential. Do not disclose another employee’s pay, request passwords, or collect full bank or tax identifiers in the assistant.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="100" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>KA-055</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Payroll Discrepancy Reporting</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>payroll</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a payroll discrepancy.
+Common questions: payroll discrepancy reporting | How do I report a payroll discrepancy? | What should I do if I need to report a payroll discrepancy? | How can I request help with payroll discrepancy reporting? | Who handles payroll discrepancy reporting?
+Guidance: Compare the relevant payslip lines with available approved records, note the pay period and discrepancy type, and route to Payroll Support for review. Do not assume the cause or promise a correction date.
+Information to include: employee identifier, pay period, discrepancy category, approximate amount only if permitted, contact method.
+Safety and approval: Payroll changes require authorized review; do not make financial adjustments or expose confidential payroll information.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="100" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>KA-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Employee Address Change</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>employee services</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request an address update.
+Common questions: employee address change | How do I request an address update? | What should I do if I need to request an address update? | How can I request help with employee address change? | Who handles employee address change?
+Guidance: Use the approved HR self-service or request channel. Provide only the fields required by HR, complete any identity verification, and check for confirmation after submission.
+Information to include: employee identifier, fields to update, effective date, authorized verification.
+Safety and approval: Personal data changes require identity verification and authorized processing; do not change records directly from a chat.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="100" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>KA-057</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Emergency Contact Update</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>employee services</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: update an emergency contact.
+Common questions: emergency contact update | How do I update an emergency contact? | What should I do if I need to update an emergency contact? | How can I request help with emergency contact update? | Who handles emergency contact update?
+Guidance: Submit the update through the approved HR process and verify the contact details before final submission. Include only the information required by the official form.
+Information to include: employee identifier, contact name, relationship, contact number, effective date.
+Safety and approval: Emergency contact details are personal information; limit access to authorized HR staff and avoid exposing them in shared channels.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="100" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>KA-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Employment Verification Letter</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request employment verification.
+Common questions: employment verification letter | How do I request employment verification? | What should I do if I need to request employment verification? | How can I request help with employment verification letter? | Who handles employment verification letter?
+Guidance: Submit a request to HR stating the purpose, recipient if applicable, and required format. HR verifies identity and employment status and issues the letter under policy.
+Information to include: employee identifier, purpose, recipient, format, required-by date.
+Safety and approval: Do not fabricate employment facts or issue official letters without HR authorization.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="100" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>KA-059</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Experience Letter Request</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request an experience letter.
+Common questions: experience letter request | How do I request an experience letter? | What should I do if I need to request an experience letter? | How can I request help with experience letter request? | Who handles experience letter request?
+Guidance: Submit a formal request through HR after checking the organization’s eligibility and separation procedures. HR confirms dates, role details, and any required approvals before issuing the document.
+Information to include: employee identifier, employment period, requested document, contact method.
+Safety and approval: Only authorized HR personnel can issue official employment documents.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="100" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>KA-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Employee Grievance Routing</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>employee relations</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: raise an employee grievance.
+Common questions: employee grievance routing | How do I raise an employee grievance? | What should I do if I need to raise an employee grievance? | How can I request help with employee grievance routing? | Who handles employee grievance routing?
+Guidance: Use the designated confidential HR or grievance channel. Describe the concern factually, include relevant dates and the outcome sought, and identify whether there is an immediate safety concern. Keep copies of the reference number.
+Information to include: summary, relevant dates, preferred confidential contact, urgency.
+Safety and approval: Do not promise confidentiality beyond policy or adjudicate allegations; route to the authorized HR or safeguarding team.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="100" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>KA-061</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>New Employee Onboarding Status</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: check onboarding task status.
+Common questions: new employee onboarding status | How do I check onboarding task status? | What should I do if I need to check onboarding task status? | How can I request help with new employee onboarding status? | Who handles new employee onboarding status?
+Guidance: Review the approved onboarding checklist and mark only tasks actually completed. Ask the assigned HR coordinator about missing items and confirm the employee’s start date and responsible manager.
+Information to include: employee identifier, joining date, department, task needing follow-up.
+Safety and approval: Do not expose another employee’s onboarding records; use role-authorized access.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="100" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>KA-062</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Employee Offboarding Checklist</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>offboarding</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: start an employee offboarding request.
+Common questions: employee offboarding checklist | How do I start an employee offboarding request? | What should I do if I need to start an employee offboarding request? | How can I request help with employee offboarding checklist? | Who handles employee offboarding checklist?
+Guidance: Notify HR through the approved process and provide the authorized separation date and manager. Coordinate equipment return, access revocation, handover, and final-pay tasks with the responsible teams.
+Information to include: employee identifier, authorized last working date, manager, handover owner.
+Safety and approval: Access revocation and employment actions require authorized human approval; do not perform them solely from an AI response.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="100" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>KA-063</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Manager Change Request</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>employee services</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request a manager record update.
+Common questions: manager change request | How do I request a manager record update? | What should I do if I need to request a manager record update? | How can I request help with manager change request? | Who handles manager change request?
+Guidance: Submit the change through HR with the effective date and appropriate authorization. HR validates the organizational change before updating records.
+Information to include: employee identifier, new manager, effective date, approval reference.
+Safety and approval: Do not infer reporting lines or change personnel records without verification.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="100" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>KA-064</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Training Course Registration</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: register for a training course.
+Common questions: training course registration | How do I register for a training course? | What should I do if I need to register for a training course? | How can I request help with training course registration? | Who handles training course registration?
+Guidance: Check eligibility, course dates, seat availability, manager approval requirements, and any cost centre rules. Submit the registration and wait for confirmation.
+Information to include: course name, session date, employee identifier, manager approval if required.
+Safety and approval: Do not claim a seat is booked until the training owner confirms it.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="100" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>KA-065</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Mandatory Training Completion</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a missing training completion record.
+Common questions: mandatory training completion | How do I report a missing training completion record? | What should I do if I need to report a missing training completion record? | How can I request help with mandatory training completion? | Who handles mandatory training completion?
+Guidance: Check the learning portal for the course and completion date. If the record is missing, send the course name and completion evidence through the authorized HR training channel.
+Information to include: employee identifier, course name, completion date, evidence reference.
+Safety and approval: Do not alter training records or mark training complete without verification.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="100" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>KA-066</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Benefits Eligibility Question</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask about employee benefits eligibility.
+Common questions: benefits eligibility question | How do I ask about employee benefits eligibility? | What should I do if I need to ask about employee benefits eligibility? | How can I request help with benefits eligibility question? | Who handles benefits eligibility question?
+Guidance: Consult the current benefits guide or Benefits Support for eligibility, enrolment windows, required documents, and effective dates. Use the official channel for personal benefit details.
+Information to include: benefit category, employment category if relevant, question, safe contact method.
+Safety and approval: Eligibility and amounts must be verified against current policy; do not reveal another employee’s benefit information.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="100" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>KA-067</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Workplace Accommodation Request</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>employee services</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request a workplace accommodation.
+Common questions: workplace accommodation request | How do I request a workplace accommodation? | What should I do if I need to request a workplace accommodation? | How can I request help with workplace accommodation request? | Who handles workplace accommodation request?
+Guidance: Contact the designated HR accommodation channel and explain the workplace adjustment requested and its work-related impact. Provide supporting documentation only through the confidential process if required.
+Information to include: requested adjustment, work impact, preferred confidential contact.
+Safety and approval: This can involve sensitive health information; do not request diagnoses in general chat or make eligibility decisions.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="100" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>KA-068</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Employee Complaint About Workplace Safety</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>employee relations</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a workplace safety concern.
+Common questions: employee complaint about workplace safety | How do I report a workplace safety concern? | What should I do if I need to report a workplace safety concern? | How can I request help with employee complaint about workplace safety? | Who handles employee complaint about workplace safety?
+Guidance: If there is immediate danger, use the site emergency procedure first. Otherwise, report the location, observed hazard, time, and immediate controls already taken to the designated safety team.
+Information to include: location, hazard description, time, immediate risk, safe contact.
+Safety and approval: Do not delay emergency response for an online request; route urgent hazards to human safety personnel.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="100" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>KA-069</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>MFA Device Lost</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a lost multi-factor authentication device.
+Common questions: mfa device lost | How do I report a lost multi-factor authentication device? | What should I do if I need to report a lost multi-factor authentication device? | How can I request help with mfa device lost? | Who handles mfa device lost?
+Guidance: Use the organization’s verified IT service channel immediately and follow identity verification and account-protection procedures. Do not approve unexpected sign-in prompts.
+Information to include: user identifier, affected service, safe callback method; no codes or passwords.
+Safety and approval: Only authorized IT staff can reset authentication factors after verification.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="100" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>KA-070</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Suspicious Login Alert</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a suspicious login alert.
+Common questions: suspicious login alert | How do I report a suspicious login alert? | What should I do if I need to report a suspicious login alert? | How can I request help with suspicious login alert? | Who handles suspicious login alert?
+Guidance: Do not approve the sign-in if it was not initiated by you. Report the alert through the approved security channel, preserve the time and alert details, and follow incident-response instructions.
+Information to include: service affected, time, alert text or reference, whether sign-in was yours.
+Safety and approval: Do not paste passwords, session tokens, or recovery codes; security staff investigate and determine containment.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="100" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>KA-071</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Phishing Email Reporting</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>security incident</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a suspected phishing email.
+Common questions: phishing email reporting | How do I report a suspected phishing email? | What should I do if I need to report a suspected phishing email? | How can I request help with phishing email reporting? | Who handles phishing email reporting?
+Guidance: Avoid clicking links or opening attachments. Use the approved report-phishing feature or forward the message as directed by security policy. Include sender and time if the reporting workflow requests it.
+Information to include: sender, time received, subject, reporting method.
+Safety and approval: Do not forward malicious content to arbitrary recipients or enter credentials on suspicious pages.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="100" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>KA-072</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Laptop Performance Problem</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a slow laptop.
+Common questions: laptop performance problem | How do I report a slow laptop? | What should I do if I need to report a slow laptop? | How can I request help with laptop performance problem? | Who handles laptop performance problem?
+Guidance: Record when the slowdown occurs, affected applications, recent changes, and any error messages. Save work, restart only if permitted, and contact IT if the issue continues. Do not install unapproved cleanup tools.
+Information to include: device asset tag, symptoms, start time, affected applications, steps tried.
+Safety and approval: Do not disable endpoint protection or change managed device settings without IT authorization.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="100" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>KA-073</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Laptop Battery or Charger Fault</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a laptop power problem.
+Common questions: laptop battery or charger fault | How do I report a laptop power problem? | What should I do if I need to report a laptop power problem? | How can I request help with laptop battery or charger fault? | Who handles laptop battery or charger fault?
+Guidance: Stop using a device or charger that is hot, swollen, sparking, or visibly damaged. Disconnect power only if it is safe to do so and contact IT or facilities through the urgent process.
+Information to include: device asset tag, charger/device symptoms, location, urgency.
+Safety and approval: Potential electrical or battery hazards require human safety handling; do not attempt to open or repair the battery.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="100" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>KA-074</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Software Installation Approval</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>software</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request software installation.
+Common questions: software installation approval | How do I request software installation? | What should I do if I need to request software installation? | How can I request help with software installation approval? | Who handles software installation approval?
+Guidance: Check the approved software catalogue first. If the software is not listed, submit its name, business purpose, vendor, licence needs, and device details for security and licensing review.
+Information to include: software name/version, business justification, device, licence requirements.
+Safety and approval: Do not install unapproved or pirated software or bypass endpoint controls.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="100" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>KA-075</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Application Error Reporting</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>software</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report an application error.
+Common questions: application error reporting | How do I report an application error? | What should I do if I need to report an application error? | How can I request help with application error reporting? | Who handles application error reporting?
+Guidance: Capture the exact error message, time, affected function, and safe reproduction steps. Remove personal or confidential data from screenshots before attaching them to the IT ticket.
+Information to include: application, error text, timestamp, impact, reproduction steps, sanitized screenshot if permitted.
+Safety and approval: Never include passwords, access tokens, patient information, or confidential data in screenshots unless an authorized secure process requires it.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="100" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>KA-076</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>VPN Connection Failure</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>network access</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a VPN connection failure.
+Common questions: vpn connection failure | How do I report a vpn connection failure? | What should I do if I need to report a vpn connection failure? | How can I request help with vpn connection failure? | Who handles vpn connection failure?
+Guidance: Confirm network access, check the official service-status channel, and use the approved VPN client. Record the error code and contact IT if the failure persists.
+Information to include: device, VPN client, error code, time, network type.
+Safety and approval: Do not disable security controls or use an unapproved VPN to bypass organizational restrictions.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="100" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>KA-077</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Shared Drive Permission Request</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>access management</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request shared drive access.
+Common questions: shared drive permission request | How do I request shared drive access? | What should I do if I need to request shared drive access? | How can I request help with shared drive permission request? | Who handles shared drive permission request?
+Guidance: Identify the specific drive or folder and the business need. Obtain the required owner or manager approval and request the minimum access level necessary.
+Information to include: folder path, read/write need, business justification, owner, approval reference.
+Safety and approval: Access must be authorized by the data owner and enforced by system permissions; never bypass access controls.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="100" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>KA-078</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Email Delivery Failure</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>communication tools</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report an email delivery failure.
+Common questions: email delivery failure | How do I report an email delivery failure? | What should I do if I need to report an email delivery failure? | How can I request help with email delivery failure? | Who handles email delivery failure?
+Guidance: Check the recipient address and whether the message generated a bounce notification. Share the bounce code with IT without resending confidential content to unapproved addresses.
+Information to include: sender, recipient domain if permitted, timestamp, bounce code, business impact.
+Safety and approval: Avoid exposing sensitive email contents; IT should verify mail routing and recipient permissions.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="100" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>KA-079</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Printer or Scanner Failure</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a printer or scanner problem.
+Common questions: printer or scanner failure | How do I report a printer or scanner problem? | What should I do if I need to report a printer or scanner problem? | How can I request help with printer or scanner failure? | Who handles printer or scanner failure?
+Guidance: Check whether the device has power and shows a visible error. Record the device location and error code, and avoid opening internal panels unless trained and authorized.
+Information to include: device location or asset tag, error code, affected users, time.
+Safety and approval: For smoke, burning smell, or electrical risk, stop using the device and report urgently.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="100" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>KA-080</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Browser Cache or Portal Issue</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>software</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: troubleshoot a web portal display issue.
+Common questions: browser cache or portal issue | How do I troubleshoot a web portal display issue? | What should I do if I need to troubleshoot a web portal display issue? | How can I request help with browser cache or portal issue? | Who handles browser cache or portal issue?
+Guidance: Record the portal, browser, time, and visible error. Follow the approved IT guide for browser refresh or supported browser checks. Do not delete business data or change security settings without authorization.
+Information to include: portal name, browser/version, error, device, steps tried.
+Safety and approval: Never ask users to share session cookies or authentication tokens.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="100" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>KA-081</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Account Lockout</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>account access</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report an account lockout.
+Common questions: account lockout | How do I report an account lockout? | What should I do if I need to report an account lockout? | How can I request help with account lockout? | Who handles account lockout?
+Guidance: Use the official account recovery process and complete identity verification. If the lockout repeats, report the approximate time and affected service so IT can investigate.
+Information to include: user identifier, service, approximate lockout time, safe contact.
+Safety and approval: Do not disclose passwords or bypass identity verification; only authorized IT can unlock accounts.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="100" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>KA-082</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>New Starter IT Setup</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request IT setup for a new starter.
+Common questions: new starter it setup | How do I request it setup for a new starter? | What should I do if I need to request it setup for a new starter? | How can I request help with new starter it setup? | Who handles new starter it setup?
+Guidance: Submit the onboarding request early enough for equipment, account, and approved application provisioning. Include the start date, role, manager, location, and approved access profile.
+Information to include: employee identifier if assigned, start date, manager, location, role, approved access.
+Safety and approval: Provision only approved minimum access after identity and manager authorization are verified.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="100" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>KA-083</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>IT Equipment Return</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: arrange return of IT equipment.
+Common questions: it equipment return | How do I arrange return of it equipment? | What should I do if I need to arrange return of it equipment? | How can I request help with it equipment return? | Who handles it equipment return?
+Guidance: Follow the IT asset-return instructions and arrange an approved drop-off or collection. Record asset tags and obtain a receipt or handover confirmation.
+Information to include: asset tag, equipment type, return date, handover method.
+Safety and approval: Do not place confidential data or unlocked devices in unsecured transport.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="100" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>KA-084</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Service Outage Reporting</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>service status</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a suspected IT service outage.
+Common questions: service outage reporting | How do I report a suspected it service outage? | What should I do if I need to report a suspected it service outage? | How can I request help with service outage reporting? | Who handles service outage reporting?
+Guidance: Check the approved service-status notice before creating duplicate reports. Report the affected service, start time, user impact, location or scope, and any error codes.
+Information to include: service, start time, scope, impact, error reference.
+Safety and approval: Do not claim an outage is confirmed until IT or the official status channel verifies it.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="100" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>KA-085</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Data Restore Request</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>data recovery</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request restoration of a work file.
+Common questions: data restore request | How do I request restoration of a work file? | What should I do if I need to request restoration of a work file? | How can I request help with data restore request? | Who handles data restore request?
+Guidance: Identify the file location, approximate last-known-good date, and business impact. Submit through the approved data recovery channel; IT checks retention and backup availability.
+Information to include: file path, owner, last-known-good date, impact, authorization.
+Safety and approval: Restoration is not guaranteed; do not access another person’s files without authorization.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="100" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>KA-086</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Security Software Alert</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>security incident</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report an endpoint security alert.
+Common questions: security software alert | How do I report an endpoint security alert? | What should I do if I need to report an endpoint security alert? | How can I request help with security software alert? | Who handles security software alert?
+Guidance: Do not dismiss or disable the alert. Record its displayed name and time and contact the security team through the approved incident channel. Follow containment instructions from authorized staff.
+Information to include: device asset tag, alert name, time, observed behaviour.
+Safety and approval: Do not investigate malware by opening suspicious files or disabling security tools.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="100" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>KA-087</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Water Leak Report</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a water leak.
+Common questions: water leak report | How do I report a water leak? | What should I do if I need to report a water leak? | How can I request help with water leak report? | Who handles water leak report?
+Guidance: If water is near electrical equipment or creates immediate danger, keep people away and use the site emergency procedure. Otherwise report the exact location, severity, time, and affected area.
+Information to include: building/room, leak severity, time, affected equipment, safe contact.
+Safety and approval: Do not enter flooded or electrically hazardous areas; facilities/safety staff assess and isolate hazards.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="100" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>KA-088</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Electrical Fault Report</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>urgent maintenance</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report an electrical fault.
+Common questions: electrical fault report | How do I report an electrical fault? | What should I do if I need to report an electrical fault? | How can I request help with electrical fault report? | Who handles electrical fault report?
+Guidance: Keep people away from exposed wiring, sparks, smoke, or wet electrical equipment. Do not touch or attempt repairs; call the site emergency or authorized facilities contact immediately.
+Information to include: exact location, observed hazard, time, people at risk.
+Safety and approval: Immediate danger requires emergency response, not ordinary ticket handling.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="100" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>KA-089</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Air Conditioning or Temperature Issue</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a temperature control issue.
+Common questions: air conditioning or temperature issue | How do I report a temperature control issue? | What should I do if I need to report a temperature control issue? | How can I request help with air conditioning or temperature issue? | Who handles air conditioning or temperature issue?
+Guidance: Report the room, observed temperature or comfort issue, time, and impact on occupants or equipment. Identify any critical equipment or vulnerable area so facilities can prioritize assessment.
+Information to include: room/location, symptoms, time, impact, affected equipment.
+Safety and approval: Do not invent safe temperature limits; use site-specific facilities and equipment requirements.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="100" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>KA-090</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Elevator or Lift Fault</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>urgent maintenance</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a lift fault.
+Common questions: elevator or lift fault | How do I report a lift fault? | What should I do if I need to report a lift fault? | How can I request help with elevator or lift fault? | Who handles elevator or lift fault?
+Guidance: If anyone is trapped or in immediate danger, use the site emergency process and the lift emergency call system. Do not force doors or attempt rescue; report the lift identifier and location.
+Information to include: building, lift identifier, observed issue, whether people are trapped.
+Safety and approval: Trapped occupants or imminent danger require immediate human emergency response.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="100" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>KA-091</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Fire Alarm or Smoke Report</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report smoke or a fire alarm concern.
+Common questions: fire alarm or smoke report | How do I report smoke or a fire alarm concern? | What should I do if I need to report smoke or a fire alarm concern? | How can I request help with fire alarm or smoke report? | Who handles fire alarm or smoke report?
+Guidance: Follow the site fire procedure, raise the alarm if required, evacuate using designated routes, and contact emergency services or the site response team. Do not investigate smoke or re-enter until authorized.
+Information to include: location, observed smoke/alarm, people at risk if safely known.
+Safety and approval: Never delay evacuation to complete a ticket; follow local emergency instructions.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="100" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>KA-092</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping Spill Request</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>cleaning</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a spill needing cleanup.
+Common questions: housekeeping spill request | How do I report a spill needing cleanup? | What should I do if I need to report a spill needing cleanup? | How can I request help with housekeeping spill request? | Who handles housekeeping spill request?
+Guidance: Identify the location and type of spill only if known safely. Keep people away and mark the area if trained and safe; report unknown chemicals or bodily fluids to the designated response team.
+Information to include: location, spill type if known, approximate size, immediate risk.
+Safety and approval: Do not touch unknown substances or clean hazardous spills without appropriate training and protective equipment.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="100" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>KA-093</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Pest Control Request</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request pest control.
+Common questions: pest control request | How do I request pest control? | What should I do if I need to request pest control? | How can I request help with pest control request? | Who handles pest control request?
+Guidance: Report the location, type of pest if safely observed, frequency, and any immediate concern. Avoid handling pests or applying unapproved chemicals; facilities arranges assessment.
+Information to include: location, observation, date/time, affected area.
+Safety and approval: Do not use unapproved pesticides, especially around patients, food, or sensitive equipment.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="100" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>KA-094</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Waste Collection or Disposal Request</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>waste management</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request waste collection.
+Common questions: waste collection or disposal request | How do I request waste collection? | What should I do if I need to request waste collection? | How can I request help with waste collection or disposal request? | Who handles waste collection or disposal request?
+Guidance: Identify the waste category and collection location using the organization’s waste segregation rules. Use designated containers and request the authorized team for special or hazardous waste.
+Information to include: waste category, location, quantity estimate, urgency.
+Safety and approval: Do not mix clinical, chemical, sharps, confidential-paper, or ordinary waste; follow approved segregation procedures.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="100" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>KA-095</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Room Setup Request</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>workspace</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request a room setup.
+Common questions: room setup request | How do I request a room setup? | What should I do if I need to request a room setup? | How can I request help with room setup request? | Who handles room setup request?
+Guidance: Provide the room, date/time, expected attendance, layout, furniture, accessibility needs, and equipment requirements. Wait for confirmation before communicating that the setup is booked.
+Information to include: room, date/time, attendance, layout, equipment, contact.
+Safety and approval: Do not block exits or fire equipment; facilities confirms feasibility and booking.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="100" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>KA-096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Building Access Door Fault</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>physical access</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a faulty access door.
+Common questions: building access door fault | How do I report a faulty access door? | What should I do if I need to report a faulty access door? | How can I request help with building access door fault? | Who handles building access door fault?
+Guidance: Report the door location, observed fault, and whether the door is stuck open or closed. If a secure area is exposed or an exit is blocked, contact site security/facilities urgently.
+Information to include: building, door/location, fault, security or egress impact.
+Safety and approval: Do not prop open secured doors or bypass access mechanisms.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="100" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>KA-097</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Workplace Hazard or Near Miss</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a workplace hazard or near miss.
+Common questions: workplace hazard or near miss | How do I report a workplace hazard or near miss? | What should I do if I need to report a workplace hazard or near miss? | How can I request help with workplace hazard or near miss? | Who handles workplace hazard or near miss?
+Guidance: If there is immediate danger, warn others if safe and follow the emergency procedure. For non-immediate hazards, report what happened, where and when, potential consequence, and temporary controls.
+Information to include: location, time, hazard, people/equipment affected, safe contact.
+Safety and approval: Do not assign blame or close the incident without review by the designated safety team.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="100" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>KA-098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Purchase Request Submission</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>purchasing</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: submit a purchase request.
+Common questions: purchase request submission | How do I submit a purchase request? | What should I do if I need to submit a purchase request? | How can I request help with purchase request submission? | Who handles purchase request submission?
+Guidance: Check the approved purchasing policy, catalogue, budget owner, and any quotation threshold. Submit the business justification, specification, quantity, required date, and cost centre for review.
+Information to include: item/service, quantity, business justification, cost centre, required date, budget owner.
+Safety and approval: Do not split purchases to avoid approval thresholds or commit funds before authorization.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="100" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>KA-099</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Supplier Onboarding</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>vendor support</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request a new supplier onboarding.
+Common questions: supplier onboarding | How do I request a new supplier onboarding? | What should I do if I need to request a new supplier onboarding? | How can I request help with supplier onboarding? | Who handles supplier onboarding?
+Guidance: Submit the supplier details through the approved vendor-management channel. Procurement and finance complete required due diligence, tax/payment verification, and approvals before the supplier is used.
+Information to include: supplier legal name, business contact, service, sponsoring department, required documents per policy.
+Safety and approval: Supplier bank details are sensitive and must be verified through approved independent procedures; do not rely solely on emailed changes.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="100" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>KA-100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Supplier Bank Detail Change</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>vendor payments</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a supplier bank detail change.
+Common questions: supplier bank detail change | How do I report a supplier bank detail change? | What should I do if I need to report a supplier bank detail change? | How can I request help with supplier bank detail change? | Who handles supplier bank detail change?
+Guidance: Treat bank-detail changes as high risk. Use the verified vendor contact already on record and the official callback or dual-approval procedure before any change is accepted.
+Information to include: supplier identifier, request reference, verification record, authorized approver.
+Safety and approval: Never update bank details based only on an email or AI instruction; fraud-prevention checks and human approval are required.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="100" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>KA-101</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>purchasing</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request supplier quotations.
+Common questions: request for quotation | How do I request supplier quotations? | What should I do if I need to request supplier quotations? | How can I request help with request for quotation? | Who handles request for quotation?
+Guidance: Provide a clear specification, quantity, delivery location/date, evaluation criteria, and budget context. Procurement determines supplier outreach and competitive-bidding requirements.
+Information to include: item/service specification, quantity, required date, delivery location, cost centre.
+Safety and approval: Follow sourcing thresholds, conflict-of-interest rules, and approved supplier processes.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="100" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>KA-102</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Invoice Status Query</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>finance operations</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask about an invoice status.
+Common questions: invoice status query | How do I ask about an invoice status? | What should I do if I need to ask about an invoice status? | How can I request help with invoice status query? | Who handles invoice status query?
+Guidance: Submit the invoice reference, supplier name, date, and the question through the authorized finance channel. Finance checks matching, approvals, disputes, and payment status.
+Information to include: invoice number, supplier, invoice date, purchase order reference if available.
+Safety and approval: Do not share full banking details or promise a payment date without finance confirmation.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="100" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>KA-103</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Invoice Mismatch</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>finance operations</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report an invoice mismatch.
+Common questions: invoice mismatch | How do I report an invoice mismatch? | What should I do if I need to report an invoice mismatch? | How can I request help with invoice mismatch? | Who handles invoice mismatch?
+Guidance: Compare the invoice against the purchase order and receipt information if authorized. Identify the mismatch type and route it to Accounts Payable or Procurement for resolution.
+Information to include: invoice reference, purchase order reference, mismatch type, supporting document reference.
+Safety and approval: Do not change invoices, approve payment, or bypass matching controls.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="100" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>KA-104</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Expense Claim Submission</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: submit an expense claim.
+Common questions: expense claim submission | How do I submit an expense claim? | What should I do if I need to submit an expense claim? | How can I request help with expense claim submission? | Who handles expense claim submission?
+Guidance: Review the current expense policy, eligible categories, submission deadlines, and receipt requirements. Enter accurate business purpose and cost centre details, attach permitted receipts, and submit for approval.
+Information to include: expense date, category, business purpose, amount/currency, cost centre, receipt.
+Safety and approval: Do not fabricate receipts or approve your own claim; reimbursements require policy checks and authorized approval.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="100" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>KA-105</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Expense Claim Rejection</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: ask why an expense claim was rejected.
+Common questions: expense claim rejection | How do I ask why an expense claim was rejected? | What should I do if I need to ask why an expense claim was rejected? | How can I request help with expense claim rejection? | Who handles expense claim rejection?
+Guidance: Review the rejection reason and policy reference. If clarification is needed, contact Finance with the claim ID and missing or disputed item; resubmit only after correcting the issue.
+Information to include: claim ID, rejection reason, question, corrected evidence if required.
+Safety and approval: Do not alter receipts or misrepresent business purpose.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="100" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>KA-106</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Budget or Cost Centre Query</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>finance operations</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask which cost centre to use.
+Common questions: budget or cost centre query | How do I ask which cost centre to use? | What should I do if I need to ask which cost centre to use? | How can I request help with budget or cost centre query? | Who handles budget or cost centre query?
+Guidance: Ask the budget owner or Finance to confirm the correct cost centre for the business purpose and department. Do not guess a code from an unrelated request.
+Information to include: department, purpose, project, budget owner, required-by date.
+Safety and approval: Financial coding and budget availability require current authoritative records.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="100" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>KA-107</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Refund or Credit Note Query</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>finance operations</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: ask about a refund or credit note.
+Common questions: refund or credit note query | How do I ask about a refund or credit note? | What should I do if I need to ask about a refund or credit note? | How can I request help with refund or credit note query? | Who handles refund or credit note query?
+Guidance: Provide the transaction or invoice reference and reason for the query. Finance verifies the credit note, matching status, and applicable process before confirming next steps.
+Information to include: invoice/reference, supplier, date, reason.
+Safety and approval: Do not promise a refund or modify accounting records without authorization.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="100" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>KA-108</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Business Travel Request</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request business travel.
+Common questions: business travel request | How do I request business travel? | What should I do if I need to request business travel? | How can I request help with business travel request? | Who handles business travel request?
+Guidance: Check the current travel policy and approval requirements before booking. Provide purpose, destination, dates, traveler details, budget/cost centre, and accessibility or scheduling needs through the approved channel.
+Information to include: business purpose, destination, dates, traveler, cost centre, approver.
+Safety and approval: Do not book or commit spend until required approval is recorded.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="100" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>KA-109</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Travel Booking Change</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request a travel booking change.
+Common questions: travel booking change | How do I request a travel booking change? | What should I do if I need to request a travel booking change? | How can I request help with travel booking change? | Who handles travel booking change?
+Guidance: Provide the booking reference, changed dates or route, reason, and urgency. Travel Desk checks fare rules, availability, cost differences, and approval requirements before confirming changes.
+Information to include: booking reference, desired change, traveler, deadline.
+Safety and approval: Do not claim a booking has changed until the travel provider or authorized desk confirms it.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="100" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>KA-110</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Travel Cancellation</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request a travel cancellation.
+Common questions: travel cancellation | How do I request a travel cancellation? | What should I do if I need to request a travel cancellation? | How can I request help with travel cancellation? | Who handles travel cancellation?
+Guidance: Submit the booking reference and reason as soon as possible. The travel desk checks cancellation deadlines, penalties, refunds, and required approvals.
+Information to include: booking reference, traveler, reason, urgency.
+Safety and approval: Refund and cancellation amounts depend on the booking terms; verify before promising an amount.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="100" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>KA-111</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Travel Safety Concern</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>travel safety</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a travel safety concern.
+Common questions: travel safety concern | How do I report a travel safety concern? | What should I do if I need to report a travel safety concern? | How can I request help with travel safety concern? | Who handles travel safety concern?
+Guidance: For immediate danger, contact local emergency services and follow the organization’s travel emergency plan. Also notify the designated travel/security contact when safe.
+Information to include: traveler contact, location if safe to share, urgency, booking reference if available.
+Safety and approval: Do not delay emergency assistance to submit an internal request; share location only with appropriate responders.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="100" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>KA-112</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Travel Expense Documentation</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask what travel expense documents are required.
+Common questions: travel expense documentation | How do I ask what travel expense documents are required? | What should I do if I need to ask what travel expense documents are required? | How can I request help with travel expense documentation? | Who handles travel expense documentation?
+Guidance: Check the current travel and expense policies for itinerary, receipts, approvals, and submission deadlines. Ask the Travel Desk or Finance to clarify any unusual expense category.
+Information to include: trip reference, expense category, travel dates, question.
+Safety and approval: Do not invent reimbursement eligibility or submit false supporting documents.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="100" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>KA-113</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Physical Security Incident</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>security incident</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a physical security incident.
+Common questions: physical security incident | How do I report a physical security incident? | What should I do if I need to report a physical security incident? | How can I request help with physical security incident? | Who handles physical security incident?
+Guidance: If anyone is in immediate danger, contact emergency services or site security. For other incidents, report the location, time, what was observed, and any safe evidence reference without confronting a suspect.
+Information to include: location, time, incident type, immediate risk, safe callback.
+Safety and approval: Do not conduct your own confrontation or investigation; preserve evidence and follow security instructions.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="100" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>KA-114</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Lost Employee Badge</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>physical access</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: report a lost employee badge.
+Common questions: lost employee badge | How do I report a lost employee badge? | What should I do if I need to report a lost employee badge? | How can I request help with lost employee badge? | Who handles lost employee badge?
+Guidance: Report the badge loss through the approved security process promptly so authorized staff can assess and disable access. Follow identity verification for replacement.
+Information to include: employee identifier, approximate loss time/location, safe contact.
+Safety and approval: Badge deactivation and replacement require authorized processing; do not share badge credentials.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="100" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>KA-115</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Visitor Access Request</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>visitor management</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request visitor access.
+Common questions: visitor access request | How do I request visitor access? | What should I do if I need to request visitor access? | How can I request help with visitor access request? | Who handles visitor access request?
+Guidance: Submit visitor name and visit details through the approved visitor-management process, including host, date/time, location, and any required pre-approval. Visitors must follow check-in and escort rules.
+Information to include: visitor details as required by official form, host, date/time, destination.
+Safety and approval: Do not bypass screening, identification, escort, or restricted-area rules.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="100" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>KA-116</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Confidential Document Sharing</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Privacy Office</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request permission to share a confidential document.
+Common questions: confidential document sharing | How do I request permission to share a confidential document? | What should I do if I need to request permission to share a confidential document? | How can I request help with confidential document sharing? | Who handles confidential document sharing?
+Guidance: Identify the document, intended recipient, business purpose, and minimum information needed. The data owner or privacy team verifies authority, approved channel, and any redaction requirements before sharing.
+Information to include: document reference, recipient, purpose, approval reference.
+Safety and approval: Do not share confidential files or links without authorization; use least-privilege access and approved secure channels.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="100" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>KA-117</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Personal Data Access Request</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Privacy Office</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: ask how to request access to personal data.
+Common questions: personal data access request | How do I ask how to request access to personal data? | What should I do if I need to ask how to request access to personal data? | How can I request help with personal data access request? | Who handles personal data access request?
+Guidance: Use the organization’s formal privacy request process. The privacy team verifies identity, scope, applicable rules, and response requirements before releasing any records.
+Information to include: requester identity through secure verification, data scope, time period, contact method.
+Safety and approval: The assistant must not disclose records directly or bypass identity verification or legal review.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="100" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>KA-118</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Personal Data Correction Request</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Privacy Office</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request correction of personal data.
+Common questions: personal data correction request | How do I request correction of personal data? | What should I do if I need to request correction of personal data? | How can I request help with personal data correction request? | Who handles personal data correction request?
+Guidance: Submit the record category, requested correction, and supporting evidence through the approved privacy or records process. The data owner verifies the request and records the outcome.
+Information to include: record category, correction requested, evidence reference, safe contact.
+Safety and approval: Do not directly alter official records or expose unrelated personal data.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="100" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>KA-119</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Suspected Data Exposure</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>Privacy Office</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>privacy incident</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a suspected data exposure.
+Common questions: suspected data exposure | How do I report a suspected data exposure? | What should I do if I need to report a suspected data exposure? | How can I request help with suspected data exposure? | Who handles suspected data exposure?
+Guidance: Report promptly through the approved privacy/security incident channel. Include what may have been exposed, where, when discovered, and containment steps already taken. Do not delete evidence or circulate the data further.
+Information to include: system/location, data category, time discovered, scope if known, safe contact.
+Safety and approval: Do not independently determine notification obligations; privacy/security personnel assess severity and response.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="100" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>KA-120</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Retention or Deletion Request</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Privacy Office</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>data handling</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask about record retention or deletion.
+Common questions: retention or deletion request | How do I ask about record retention or deletion? | What should I do if I need to ask about record retention or deletion? | How can I request help with retention or deletion request? | Who handles retention or deletion request?
+Guidance: Identify the record category and business context. The authorized records/privacy owner checks retention schedules, legal holds, and approvals before any deletion or disposal.
+Information to include: record category, system/location, reason, authorization reference.
+Safety and approval: Never permanently delete records merely because a user asks; irreversible actions require authorization and human review.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="100" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>KA-121</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Audit Evidence Request</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request audit evidence.
+Common questions: audit evidence request | How do I request audit evidence? | What should I do if I need to request audit evidence? | How can I request help with audit evidence request? | Who handles audit evidence request?
+Guidance: Specify the audit purpose, period, system, evidence type, and authorized request reference. The system owner or audit team provides the minimum approved evidence and logs access as required.
+Information to include: audit reference, time period, system, evidence requested, approver.
+Safety and approval: Do not alter audit logs or disclose restricted evidence to unauthorized users.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="100" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>KA-122</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Access Review Request</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>access management</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request an access review.
+Common questions: access review request | How do I request an access review? | What should I do if I need to request an access review? | How can I request help with access review request? | Who handles access review request?
+Guidance: Identify the system, role, and business need. The system owner or manager reviews current permissions and approves any changes through the official workflow.
+Information to include: user identifier, system, role, business justification, manager/owner approval.
+Safety and approval: Do not grant elevated access based only on a chat request; enforce least privilege and human approval.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="100" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>KA-123</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>How to Write a Good Support Request</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>service desk</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: submit a complete support request.
+Common questions: how to write a good support request | How do I submit a complete support request? | What should I do if I need to submit a complete support request? | How can I request help with how to write a good support request? | Who handles how to write a good support request?
+Guidance: Describe one issue per request where practical. State the affected service, expected versus actual behaviour, time started, business impact, error message, steps already tried, and how support can contact you. Do not include secrets.
+Information to include: service, concise summary, impact, timestamp, safe evidence, contact method.
+Safety and approval: Redact passwords, tokens, patient details, payroll data, and unrelated personal information.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="100" customHeight="1">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>KA-124</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Choosing Request Priority</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>service desk</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: choose a request priority.
+Common questions: choosing request priority | How do I choose a request priority? | What should I do if I need to choose a request priority? | How can I request help with choosing request priority? | Who handles choosing request priority?
+Guidance: Describe the actual business impact, number of users or services affected, time sensitivity, and any safety or security concern. The service desk applies the organization’s priority matrix; users should not exaggerate impact to jump the queue.
+Information to include: impact, scope, start time, workaround, safety/security impact.
+Safety and approval: Priority labels and response targets must follow the current approved SLA matrix; the assistant does not guarantee resolution times.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="100" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>KA-125</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Critical Incident Escalation</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>escalation</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: escalate a critical operational incident.
+Common questions: critical incident escalation | How do I escalate a critical operational incident? | What should I do if I need to escalate a critical operational incident? | How can I request help with critical incident escalation? | Who handles critical incident escalation?
+Guidance: If there is immediate risk to life, safety, or security, use the emergency response channel first. For critical service disruption, contact the designated incident lead and submit the incident reference, impact, timeline, and actions taken.
+Information to include: incident reference, service, impact, start time, incident lead, actions taken.
+Safety and approval: Do not rely only on a chatbot for emergencies; human incident command owns decisions and communications.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="100" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>KA-126</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Request Status Definitions</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>service desk</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: understand support request statuses.
+Common questions: request status definitions | How do I understand support request statuses? | What should I do if I need to understand support request statuses? | How can I request help with request status definitions? | Who handles request status definitions?
+Guidance: Common examples may include New (received), In Progress (being handled), Waiting for Information (requester input needed), Pending Approval (approval outstanding), Escalated (specialist review), and Resolved (work reported complete). The actual application’s displayed status and local definitions take precedence.
+Information to include: request ID, current status, requested clarification.
+Safety and approval: Do not claim a status changed unless confirmed by the request system.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="100" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>KA-127</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Pending Information Follow-up</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>service desk</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: respond to a request for more information.
+Common questions: pending information follow-up | How do I respond to a request for more information? | What should I do if I need to respond to a request for more information? | How can I request help with pending information follow-up? | Who handles pending information follow-up?
+Guidance: Open the request using the official application, read the requested fields, and reply with only the necessary information. If you cannot provide it, explain why and ask the assigned team what alternatives are accepted.
+Information to include: request ID, requested fields, safe response.
+Safety and approval: Never provide passwords, authentication codes, or unrelated confidential data to satisfy a support request.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="100" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>KA-128</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>SLA Target Explanation</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>SLA</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: understand an SLA target.
+Common questions: sla target explanation | How do I understand an sla target? | What should I do if I need to understand an sla target? | How can I request help with sla target explanation? | Who handles sla target explanation?
+Guidance: An SLA target is a service commitment or internal goal defined by the organization, often measured by priority and business hours. Check the current SLA policy for when the clock starts, pauses, and stops; distinguish first response from full resolution.
+Information to include: request ID, priority, submission time, applicable service.
+Safety and approval: Configured demo targets are not a guarantee. The application’s current policy and service team determine applicable targets.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="100" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>KA-129</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Duplicate Support Request</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>service desk</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a duplicate support request.
+Common questions: duplicate support request | How do I report a duplicate support request? | What should I do if I need to report a duplicate support request? | How can I request help with duplicate support request? | Who handles duplicate support request?
+Guidance: Search for an existing request before creating another. If one exists, add new evidence to it or ask support to link duplicates so that updates and ownership remain consistent.
+Information to include: existing request ID, new information, affected service.
+Safety and approval: Do not close a duplicate automatically if it contains unique information or an active safety concern.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="100" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>KA-130</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Reopen a Resolved Request</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>service desk</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask to reopen a resolved request.
+Common questions: reopen a resolved request | How do I ask to reopen a resolved request? | What should I do if I need to ask to reopen a resolved request? | How can I request help with reopen a resolved request? | Who handles reopen a resolved request?
+Guidance: Use the official request workflow and explain why the issue persists or has returned. Include when it recurred and any new evidence. The assigned team determines whether to reopen or create a linked request.
+Information to include: request ID, recurrence time, current impact, evidence.
+Safety and approval: Do not state that a request has been reopened until the system confirms it.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="100" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>KA-131</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Request Feedback or Incorrect AI Answer</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>AI feedback</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report an incorrect assistant answer.
+Common questions: request feedback or incorrect ai answer | How do I report an incorrect assistant answer? | What should I do if I need to report an incorrect assistant answer? | How can I request help with request feedback or incorrect ai answer? | Who handles request feedback or incorrect ai answer?
+Guidance: Submit the question, the answer’s issue type, and the source or article reference if shown. Remove confidential information from the feedback. The knowledge owner reviews and updates approved content when appropriate.
+Information to include: question, issue type, article/source reference, sanitized details.
+Safety and approval: Feedback is not proof that an article is wrong; changes require review and version control.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="100" customHeight="1">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>KA-132</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Knowledge Article Maintenance</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>knowledge management</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request a knowledge article update.
+Common questions: knowledge article maintenance | How do I request a knowledge article update? | What should I do if I need to request a knowledge article update? | How can I request help with knowledge article maintenance? | Who handles knowledge article maintenance?
+Guidance: Identify the article, the incorrect or missing information, the proposed correction, and a reliable policy/source owner. A reviewer verifies the change, updates the effective date/version, and approves it before retrieval.
+Information to include: article ID/title, proposed change, authoritative source, reviewer/owner.
+Safety and approval: Do not mark unverified or obsolete content as approved; preserve auditability and resolve conflicting sources with the owner.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="100" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>KA-133</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Assistant Cannot Find an Answer</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>AI knowledge</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: handle an unsupported assistant question.
+Common questions: assistant cannot find an answer | How do I handle an unsupported assistant question? | What should I do if I need to handle an unsupported assistant question? | How can I request help with assistant cannot find an answer? | Who handles assistant cannot find an answer?
+Guidance: Rephrase the question with the service name, department, task, and relevant terms. If the answer is still unsupported, submit a knowledge-gap feedback request or contact the responsible team. The assistant should say when approved sources do not provide the answer.
+Information to include: question, expected topic, department, source that may contain the answer.
+Safety and approval: Do not invent a policy, deadline, contact, or operational action to fill a knowledge gap.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="100" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>KA-134</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Department Ownership Lookup</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: find the right team for an operational issue.
+Common questions: department ownership lookup | How do I find the right team for an operational issue? | What should I do if I need to find the right team for an operational issue? | How can I request help with department ownership lookup? | Who handles department ownership lookup?
+Guidance: Describe the issue, affected service, location, and impact. The application’s approved request-type and routing rules identify the likely team; if no matching rule exists, route to the service desk for human triage.
+Information to include: issue summary, department/location, service, impact.
+Safety and approval: Do not assume a team assignment where the routing catalogue is missing or ambiguous.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="100" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>KA-135</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Request Cancellation</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>service desk</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request cancellation of an open support request.
+Common questions: request cancellation | How do I request cancellation of an open support request? | What should I do if I need to request cancellation of an open support request? | How can I request help with request cancellation? | Who handles request cancellation?
+Guidance: Open the request and use the approved cancellation function or contact the assigned team. State why it is no longer needed and confirm whether any work, purchase, or access change is already in progress.
+Information to include: request ID, cancellation reason, requester confirmation.
+Safety and approval: Cancellation may not reverse work already performed; financial, access, and safety actions need human review.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="100" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>KA-136</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Human Approval Required</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: understand why a request needs human approval.
+Common questions: human approval required | How do I understand why a request needs human approval? | What should I do if I need to understand why a request needs human approval? | How can I request help with human approval required? | Who handles human approval required?
+Guidance: Some requests affect access, money, employment records, confidential data, or irreversible operations. The system collects required information and routes it to an authorized approver; it should not treat AI guidance as approval.
+Information to include: request ID, action requested, approval owner if known.
+Safety and approval: No bypass of access controls, approval steps, or audit requirements.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="100" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>KA-137</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>System Status and Outage Communication</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>service status</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: ask whether a system is down.
+Common questions: system status and outage communication | How do I ask whether a system is down? | What should I do if I need to ask whether a system is down? | How can I request help with system status and outage communication? | Who handles system status and outage communication?
+Guidance: Check the official service-status page or incident notice. If no confirmed notice exists, report your symptoms and avoid stating that an outage is confirmed. Follow official updates for workarounds and recovery.
+Information to include: system, error, time, location/scope, official incident reference if available.
+Safety and approval: The assistant cannot infer live service health from static knowledge articles.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="100" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>KA-138</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Workaround Documentation</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>incident management</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: document a temporary workaround.
+Common questions: workaround documentation | How do I document a temporary workaround? | What should I do if I need to document a temporary workaround? | How can I request help with workaround documentation? | Who handles workaround documentation?
+Guidance: Describe the approved workaround, affected version or system, prerequisites, known limitations, and rollback or stop conditions. Have the service owner approve it before broad distribution.
+Information to include: incident/change reference, owner, scope, limitations, approval.
+Safety and approval: Do not recommend unsafe or unapproved workarounds that weaken security or compromise records.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="100" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>KA-139</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>Shift Handover Note</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>handover</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: prepare an operational shift handover.
+Common questions: shift handover note | How do I prepare an operational shift handover? | What should I do if I need to prepare an operational shift handover? | How can I request help with shift handover note? | Who handles shift handover note?
+Guidance: Summarize open incidents, current impact, actions taken, next steps, owners, deadlines, and escalation contacts. Use the approved handover system and include only information the next shift needs.
+Information to include: incident/request IDs, status, owner, next action, time sensitivity.
+Safety and approval: Exclude unnecessary patient or employee identifiers and never share credentials.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="100" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>KA-140</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Business Continuity Procedure Lookup</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>business continuity</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: find business continuity instructions.
+Common questions: business continuity procedure lookup | How do I find business continuity instructions? | What should I do if I need to find business continuity instructions? | How can I request help with business continuity procedure lookup? | Who handles business continuity procedure lookup?
+Guidance: Identify the service or site affected and consult the current approved continuity plan. Follow the named incident lead and documented fallback process; if the plan cannot be located, contact the designated continuity owner.
+Information to include: service/site, disruption, impact, continuity plan reference if known.
+Safety and approval: Do not invent downtime procedures or make safety-critical decisions without the responsible human lead.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="100" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>KA-141</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Change Request Guidance</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>change management</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request a system change.
+Common questions: change request guidance | How do I request a system change? | What should I do if I need to request a system change? | How can I request help with change request guidance? | Who handles change request guidance?
+Guidance: Describe the proposed change, business reason, scope, affected systems, risks, testing, implementation window, rollback plan, and owner. Submit it for the organization’s change review and wait for approval before implementation.
+Information to include: change summary, reason, scope, risk, test and rollback plan, owner.
+Safety and approval: Do not deploy changes or alter production systems without the required approval.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="100" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>KA-142</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Planned Maintenance Notice</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>service status</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask about planned maintenance.
+Common questions: planned maintenance notice | How do I ask about planned maintenance? | What should I do if I need to ask about planned maintenance? | How can I request help with planned maintenance notice? | Who handles planned maintenance notice?
+Guidance: Check the official maintenance notice for affected services, window, expected impact, and contact channel. If the notice is missing or unclear, ask the service owner; do not infer dates from old announcements.
+Information to include: service, notice reference, time zone, question.
+Safety and approval: Only current official notices confirm maintenance schedules.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="100" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>KA-143</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Data Quality Correction</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>data quality</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report an incorrect operational record.
+Common questions: data quality correction | How do I report an incorrect operational record? | What should I do if I need to report an incorrect operational record? | How can I request help with data quality correction? | Who handles data quality correction?
+Guidance: Identify the record reference, field, observed value, expected value, and authoritative evidence. Submit to the data owner, who verifies the correction and preserves the audit trail.
+Information to include: record reference, field, proposed correction, evidence, owner.
+Safety and approval: Do not overwrite official records or change data based only on an unverified claim.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="100" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>KA-144</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metrics Definition</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask how an operational metric is defined.
+Common questions: operational metrics definition | How do I ask how an operational metric is defined? | What should I do if I need to ask how an operational metric is defined? | How can I request help with operational metrics definition? | Who handles operational metrics definition?
+Guidance: Use the metric dictionary or dashboard documentation to confirm numerator, denominator, time window, exclusions, refresh cadence, and owner. If definitions are missing, ask the reporting owner rather than guessing.
+Information to include: metric name, dashboard, reporting period, question.
+Safety and approval: Do not present a metric as official if its definition or data freshness is unknown.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="100" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>KA-145</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>Report Access Request</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request access to an operational report.
+Common questions: report access request | How do I request access to an operational report? | What should I do if I need to request access to an operational report? | How can I request help with report access request? | Who handles report access request?
+Guidance: State the report name, business purpose, required level of access, and data scope. The report owner checks authorization and grants the minimum approved access.
+Information to include: report name, purpose, read/export need, manager/owner approval.
+Safety and approval: Report access may expose sensitive data; export permissions need separate review where applicable.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="100" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>KA-146</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Meeting Minutes and Action Tracking</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>collaboration</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: record operational meeting actions.
+Common questions: meeting minutes and action tracking | How do I record operational meeting actions? | What should I do if I need to record operational meeting actions? | How can I request help with meeting minutes and action tracking? | Who handles meeting minutes and action tracking?
+Guidance: Capture decisions, action owner, due date, dependencies, and unresolved questions. Circulate minutes only to the intended audience and store them in the approved location.
+Information to include: meeting name/date, decisions, actions, owners, due dates.
+Safety and approval: Do not include sensitive personnel or patient details unless necessary and authorized.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="100" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>KA-147</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>Vendor Service Issue</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>vendor support</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a vendor service issue.
+Common questions: vendor service issue | How do I report a vendor service issue? | What should I do if I need to report a vendor service issue? | How can I request help with vendor service issue? | Who handles vendor service issue?
+Guidance: Record the contract or purchase order reference, service impact, dates, evidence, and prior contact. Route to the vendor owner or procurement team to check service terms and next steps.
+Information to include: vendor, contract/PO reference, issue, dates, impact, contact history.
+Safety and approval: Do not make legal commitments or promise penalties/credits without contract-owner review.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="100" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>KA-148</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Contract Renewal Reminder</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>vendor management</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask about a contract renewal.
+Common questions: contract renewal reminder | How do I ask about a contract renewal? | What should I do if I need to ask about a contract renewal? | How can I request help with contract renewal reminder? | Who handles contract renewal reminder?
+Guidance: Provide the contract reference, supplier, renewal/expiry date if known, business owner, and decision needed. Procurement or Legal verifies notice periods, options, and approval requirements.
+Information to include: contract reference, supplier, owner, expiry date, decision deadline.
+Safety and approval: Do not infer contract terms or automatically renew/cancel an agreement.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="100" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>KA-149</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>Records Filing and Naming</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>records management</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: ask how to file an operational document.
+Common questions: records filing and naming | How do I ask how to file an operational document? | What should I do if I need to ask how to file an operational document? | How can I request help with records filing and naming? | Who handles records filing and naming?
+Guidance: Use the approved repository, naming convention, metadata fields, access classification, and retention category. If no standard is published, ask the records owner before storing restricted content.
+Information to include: document type, repository, business unit, classification.
+Safety and approval: Do not store confidential documents in personal drives or unapproved services.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="100" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>KA-150</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility Support Request</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>accessibility</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: request accessibility support for a workplace visit.
+Common questions: accessibility support request | How do I request accessibility support for a workplace visit? | What should I do if I need to request accessibility support for a workplace visit? | How can I request help with accessibility support request? | Who handles accessibility support request?
+Guidance: State the location, date/time, barrier, and requested practical adjustment through the designated facilities or accessibility channel. The responsible team confirms feasibility and any follow-up.
+Information to include: location, date/time, requested adjustment, safe contact.
+Safety and approval: Do not ask for unnecessary medical details or guarantee accommodation before confirmation.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="100" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t>KA-151</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>Food Service or Catering Issue</t>
+        </is>
+      </c>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>catering</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report a catering issue.
+Common questions: food service or catering issue | How do I report a catering issue? | What should I do if I need to report a catering issue? | How can I request help with food service or catering issue? | Who handles food service or catering issue?
+Guidance: Report the service location, time, order or event reference, issue type, and immediate food safety concern if any. For suspected contamination or allergic reaction, follow emergency/site food safety procedures immediately.
+Information to include: location, event/order reference, issue, time, impact.
+Safety and approval: Do not provide medical advice; urgent allergic reactions require emergency response.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="100" customHeight="1">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>KA-152</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Advice Boundary</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Support</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>clinical safety</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask what to do about a patient’s symptoms.
+Common questions: clinical advice boundary | How do I ask what to do about a patient’s symptoms? | What should I do if I need to ask what to do about a patient’s symptoms? | How can I request help with clinical advice boundary? | Who handles clinical advice boundary?
+Guidance: The assistant is for operational support, not diagnosis, treatment, medication selection, or interpretation of patient symptoms. Contact a qualified clinician and follow the approved clinical escalation or emergency protocol.
+Information to include: operational routing need only; do not enter patient details into general chat.
+Safety and approval: Never provide patient-specific medical advice, medication or dosage recommendations, or delay emergency care.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="100" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>KA-153</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Patient Record Access Boundary</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>Privacy Office</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: request access to a patient record.
+Common questions: patient record access boundary | How do I request access to a patient record? | What should I do if I need to request access to a patient record? | How can I request help with patient record access boundary? | Who handles patient record access boundary?
+Guidance: Use the organization’s authorized clinical record system and established identity, role, purpose-of-use, and audit requirements. If access is needed for a legitimate task, request it through the designated access process.
+Information to include: system/role request and authorization reference, not patient details in general chat.
+Safety and approval: The assistant must not retrieve or disclose patient records, bypass permissions, or expose protected information.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="100" customHeight="1">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>KA-154</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Medication or Prescription Request Boundary</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Support</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>clinical safety</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: ask for a medication or dosage recommendation.
+Common questions: medication or prescription request boundary | How do I ask for a medication or dosage recommendation? | What should I do if I need to ask for a medication or dosage recommendation? | How can I request help with medication or prescription request boundary? | Who handles medication or prescription request boundary?
+Guidance: The assistant cannot recommend or prescribe a medication or dosage. Refer the question to a licensed clinician or pharmacist through the approved clinical workflow; for an emergency, use the emergency response process.
+Information to include: only the operational team or escalation channel needed.
+Safety and approval: Do not provide treatment instructions or substitute for qualified clinical judgment.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="100" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>KA-155</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>Emergency Event Reporting</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: report an emergency event.
+Common questions: emergency event reporting | How do I report an emergency event? | What should I do if I need to report an emergency event? | How can I request help with emergency event reporting? | Who handles emergency event reporting?
+Guidance: Contact local emergency services and activate the site’s emergency plan when there is immediate danger. After immediate response is underway, use the approved incident reporting channel to document facts and actions.
+Information to include: location, event type, immediate danger, response reference if safe.
+Safety and approval: The chatbot is not an emergency dispatch service; do not wait for an AI response.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I156" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="100" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>KA-156</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Conflicting Knowledge Sources</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>knowledge management</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>Purpose: resolve conflicting procedure documents.
+Common questions: conflicting knowledge sources | How do I resolve conflicting procedure documents? | What should I do if I need to resolve conflicting procedure documents? | How can I request help with conflicting knowledge sources? | Who handles conflicting knowledge sources?
+Guidance: Check source owner, approval status, effective date, version, and scope. Do not combine conflicting instructions into a new policy; escalate to the accountable policy owner and use only the currently approved source.
+Information to include: article IDs, document titles, conflict description, business area.
+Safety and approval: Do not guess which policy wins; unverified or obsolete content should not be treated as authoritative.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="100" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>KA-157</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>Out-of-Scope Question Handling</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>AI governance</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>Purpose: handle a question outside the assistant’s scope.
+Common questions: out-of-scope question handling | How do I handle a question outside the assistant’s scope? | What should I do if I need to handle a question outside the assistant’s scope? | How can I request help with out-of-scope question handling? | Who handles out-of-scope question handling?
+Guidance: The assistant should explain that it lacks an approved source or the request is outside healthcare operations. It may suggest the appropriate authorized team, but it must not fabricate an answer.
+Information to include: question topic, relevant department if known.
+Safety and approval: Do not answer unrelated, high-risk, clinical, confidential, or unsupported questions as if verified.
+If the steps do not resolve the issue, submit an operational support request with the service, department, impact, time observed, steps already tried, and a safe contact method. Do not include passwords, one-time codes, or unnecessary personal or patient information. The assigned team should verify current local policy before taking action.</t>
+        </is>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic operational guidance — verify against current local policy before production use</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I158" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I51"/>
+  <autoFilter ref="A1:I158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
